--- a/data/item_list.xlsx
+++ b/data/item_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tanaka\Desktop\Python\PokemonAutoCapture\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A703DCDF-C7AE-4CBA-AA8F-15F34F1D7109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D494C4FC-8EA8-4BD7-8603-B3972EF36412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2067" uniqueCount="1557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2067" uniqueCount="1558">
   <si>
     <t>File Name</t>
   </si>
@@ -5214,6 +5214,10 @@
   </si>
   <si>
     <t>Index</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>こだわりスカーフ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -7927,7 +7931,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>682</v>
+        <v>1557</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>213</v>
